--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -29,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,6 +97,21 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://psa.gov.ph/classification/psced/level</t>
   </si>
 </sst>
 </file>
@@ -355,4 +371,44 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,10 +100,31 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>C201301</t>
+  </si>
+  <si>
+    <t>Elementary Graduate</t>
+  </si>
+  <si>
+    <t>C201302</t>
+  </si>
+  <si>
+    <t>High School Graduate</t>
+  </si>
+  <si>
+    <t>C201303</t>
+  </si>
+  <si>
+    <t>College Graduate</t>
+  </si>
+  <si>
+    <t>C201304</t>
+  </si>
+  <si>
+    <t>Postgraduate</t>
   </si>
   <si>
     <t/>
@@ -112,6 +134,33 @@
   </si>
   <si>
     <t>https://psa.gov.ph/classification/psced/level</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>false</t>
   </si>
 </sst>
 </file>
@@ -375,7 +424,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -386,26 +435,173 @@
       <c r="A1" t="s" s="1">
         <v>28</v>
       </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
         <v>31</v>
       </c>
+      <c r="E3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>47</v>
+      </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-educational-attainments.xlsx
+++ b/dev/ValueSet-educational-attainments.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
